--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_64943_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_64943_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2d8f45f80bcc407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra8ae2d7fc5d74f9f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,51 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4888</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_64943_completo.xlsx
+++ b/13158_Cuenca_Sama/_raw_reportes_xlsx/IDConfig_64943_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra8ae2d7fc5d74f9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7f1f771f41294c0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,816 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5763</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8153</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0005</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1035</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3305</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6943</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2155</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8586</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1648</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3589</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6217</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4157</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2827</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4718</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7974</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9930</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9199</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1827</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9109</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5366</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2245</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0184</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1005</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8786</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8054</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4784</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6441</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6158</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4366</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0483</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0826</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>17/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.1650</x:v>
+        <x:v>      1.0304</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2170</x:v>
+        <x:v>      1.2245</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4888</x:v>
+        <x:v>      1.4754</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.5381</x:v>
+        <x:v>      1.5442</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4142</x:v>
+        <x:v>      1.4246</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4106</x:v>
+        <x:v>      1.0781</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.8198</x:v>
+        <x:v>      0.6167</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.7650</x:v>
+        <x:v>      0.7033</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.9686</x:v>
+        <x:v>      0.8646</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3036</x:v>
+        <x:v>      1.2648</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.6949</x:v>
+        <x:v>      1.6448</x:v>
       </x:c>
     </x:row>
     <x:row>
